--- a/Questions - Round 3.xlsx
+++ b/Questions - Round 3.xlsx
@@ -1,14 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_03E6B4E8F44C5BCDCDAD4B92FE3242ACE4F5FCDD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{15858584-32AA-4FDF-BFC3-8592CB3CBC55}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://innochemnv-my.sharepoint.com/personal/zander_fias_innochem_be/Documents/OneDrive_1_25-9-2026/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="91" documentId="11_03E6B4E8F44C5BCDCDAD4B92FE3242ACE4F5FCDD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A40DD598-176B-4C5A-B5B5-F4B4B555D5EB}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EN" sheetId="1" r:id="rId1"/>
+    <sheet name="NL" sheetId="2" r:id="rId2"/>
+    <sheet name="FR" sheetId="3" r:id="rId3"/>
+    <sheet name="GE" sheetId="4" r:id="rId4"/>
+    <sheet name="SP" sheetId="5" r:id="rId5"/>
+    <sheet name="IT" sheetId="6" r:id="rId6"/>
+    <sheet name="PL" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -31,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="606" uniqueCount="428">
   <si>
     <t>type</t>
   </si>
@@ -253,13 +264,1075 @@
   </si>
   <si>
     <t>Respectful challenge can help change everyday norms. Personal habits matter because many small choices become meaningful when repeated by many people.</t>
+  </si>
+  <si>
+    <t>Wat is de hoofdgedachte achter SDG 5 – Gendergelijkheid?</t>
+  </si>
+  <si>
+    <t>Gemakkelijk · Enkele keuze</t>
+  </si>
+  <si>
+    <t>Het is alleen van toepassing op nationale overheden.</t>
+  </si>
+  <si>
+    <t>Het is slechts een marketingslogan zonder praktische betekenis.</t>
+  </si>
+  <si>
+    <t>Het richt zich op gelijke kansen en empowerment.</t>
+  </si>
+  <si>
+    <t>Het vraagt bedrijven om langetermijneffecten te negeren.</t>
+  </si>
+  <si>
+    <t>SDG 5 gaat over gelijke kansen en empowerment en over het omzetten van dat doel in praktische actie. SDG 5 wordt nuttig wanneer mensen het brede doel vertalen naar praktische beslissingen.</t>
+  </si>
+  <si>
+    <t>Waarom is SDG 5 relevant voor een bedrijf dat chemische producten distribueert en produceert?</t>
+  </si>
+  <si>
+    <t>Gemiddeld · Enkele keuze</t>
+  </si>
+  <si>
+    <t>Omdat duurzaamheid alleen in jaarverslagen thuishoort.</t>
+  </si>
+  <si>
+    <t>Omdat chemische producten geen verband houden met duurzaamheid.</t>
+  </si>
+  <si>
+    <t>Omdat de SDG's alle wettelijke vereisten vervangen.</t>
+  </si>
+  <si>
+    <t>Omdat diverse teams en eerlijke loopbaankansen de duurzaamheidsprestaties kunnen beïnvloeden.</t>
+  </si>
+  <si>
+    <t>Diverse teams en eerlijke loopbaankansen zijn praktische gebieden waarop een bedrijf een verschil kan maken. De SDG's verbinden wereldwijde doelen met dagelijkse operationele keuzes.</t>
+  </si>
+  <si>
+    <t>Welke uitspraak is een veelvoorkomend misverstand over SDG 5?</t>
+  </si>
+  <si>
+    <t>Gendergelijkheid betekent dat de ene groep boven de andere wordt bevoordeeld.</t>
+  </si>
+  <si>
+    <t>Medewerkers kunnen bijdragen via kleine gewoonten.</t>
+  </si>
+  <si>
+    <t>Bedrijven kunnen relevante effecten meten en verbeteren.</t>
+  </si>
+  <si>
+    <t>SDG 5 kan worden gekoppeld aan dagelijkse beslissingen.</t>
+  </si>
+  <si>
+    <t>Dit is het misverstand: het maakt de SDG te eng en verbergt praktische kansen. Een goede quizvraag daagt vaak een misvatting uit, omdat dit de leerervaring beter doet beklijven.</t>
+  </si>
+  <si>
+    <t>Welk gedrag zet SDG 5 het best om van theorie naar actie?</t>
+  </si>
+  <si>
+    <t>Over duurzaamheid praten maar niets veranderen.</t>
+  </si>
+  <si>
+    <t>Een concrete verbetering kiezen en die uitvoeren.</t>
+  </si>
+  <si>
+    <t>Wachten tot iemand anders alles oplost.</t>
+  </si>
+  <si>
+    <t>Het tegenovergestelde doen wanneer niemand kijkt.</t>
+  </si>
+  <si>
+    <t>Concrete actie zorgt voor leren en meetbare verbetering. Bewustzijn rond duurzaamheid moet leiden tot praktische gedragsverandering.</t>
+  </si>
+  <si>
+    <t>Wat maakt SDG 5 tot een nuttig leerthema voor medewerkers?</t>
+  </si>
+  <si>
+    <t>Het houdt geen verband met de bedrijfscultuur.</t>
+  </si>
+  <si>
+    <t>Het biedt één perfect antwoord voor elke situatie.</t>
+  </si>
+  <si>
+    <t>Het verbindt wereldwijde uitdagingen met keuzes die mensen herkennen op het werk en thuis.</t>
+  </si>
+  <si>
+    <t>Het maakt deskundige kennis overbodig.</t>
+  </si>
+  <si>
+    <t>De krachtigste leerervaring ontstaat wanneer mensen het verband zien tussen wereldwijde doelen en vertrouwde keuzes. De SDG's zijn het meest boeiend wanneer ze relevant en concreet aanvoelen en aansluiten bij de rollen van mensen.</t>
+  </si>
+  <si>
+    <t>Wat is Women@STOCKMEIER?</t>
+  </si>
+  <si>
+    <t>Een kortingsprogramma voor klanten</t>
+  </si>
+  <si>
+    <t>Een technisch opslagsysteem</t>
+  </si>
+  <si>
+    <t>Uitsluitend een wettelijk rapportageformulier</t>
+  </si>
+  <si>
+    <t>Een intern netwerk dat professionele ontwikkeling, uitwisseling en gelijke kansen ondersteunt</t>
+  </si>
+  <si>
+    <t>Het rapport beschrijft Women@STOCKMEIER als een intern netwerk dat de ontwikkeling, uitwisseling en zichtbaarheid van vrouwen ondersteunt. Voorbeelden van STOCKMEIER maken de SDG concreet en tonen hoe groepsinitiatieven aansluiten bij wereldwijde doelen.</t>
+  </si>
+  <si>
+    <t>Welk aandeel van de topmanagementfuncties op groepsniveau wordt volgens het rapport door vrouwen bekleed?</t>
+  </si>
+  <si>
+    <t>Moeilijk · Enkele keuze</t>
+  </si>
+  <si>
+    <t>Het rapport vermeldt dat vrouwen 27% van de topmanagementfuncties bekleden. Voorbeelden van STOCKMEIER maken de SDG concreet en tonen hoe groepsinitiatieven aansluiten bij wereldwijde doelen.</t>
+  </si>
+  <si>
+    <t>Welke toekomstige focus wordt genoemd in verband met gendergelijkheid?</t>
+  </si>
+  <si>
+    <t>Alleen het magazijnvolume meten</t>
+  </si>
+  <si>
+    <t>Gerichte ondersteuningsprogramma's en transparante loopbaanpaden</t>
+  </si>
+  <si>
+    <t>Alle opleidingen afschaffen</t>
+  </si>
+  <si>
+    <t>Leiderschapsontwikkeling vermijden</t>
+  </si>
+  <si>
+    <t>Het rapport noemt gerichte ondersteuningsprogramma's, transparante loopbaanpaden en een ondersteunende bedrijfscultuur. Voorbeelden van STOCKMEIER maken de SDG concreet en tonen hoe groepsinitiatieven aansluiten bij wereldwijde doelen.</t>
+  </si>
+  <si>
+    <t>Welke actie thuis of in het sociale leven ondersteunt SDG 5?</t>
+  </si>
+  <si>
+    <t>Ongelijke behandeling negeren</t>
+  </si>
+  <si>
+    <t>Taken toewijzen op basis van stereotypen</t>
+  </si>
+  <si>
+    <t>Huishoudelijke verantwoordelijkheden eerlijk verdelen</t>
+  </si>
+  <si>
+    <t>Mensen ontmoedigen om nieuwe vaardigheden te leren</t>
+  </si>
+  <si>
+    <t>Een eerlijke verdeling van verantwoordelijkheden ondersteunt gelijke kansen. Persoonlijke gewoonten zijn belangrijk, omdat veel kleine keuzes betekenisvol worden wanneer veel mensen ze herhalen.</t>
+  </si>
+  <si>
+    <t>Wat kan iemand doen wanneer die een bevooroordeelde opmerking hoort?</t>
+  </si>
+  <si>
+    <t>Altijd zwijgen</t>
+  </si>
+  <si>
+    <t>Lachen om de opmerking aan te moedigen</t>
+  </si>
+  <si>
+    <t>De opmerking luider herhalen</t>
+  </si>
+  <si>
+    <t>De opmerking respectvol ter discussie stellen of een doordachte vraag stellen</t>
+  </si>
+  <si>
+    <t>Respectvol reageren kan dagelijkse normen helpen veranderen. Persoonlijke gewoonten zijn belangrijk, omdat veel kleine keuzes betekenisvol worden wanneer veel mensen ze herhalen.</t>
+  </si>
+  <si>
+    <t>Quelle est l'idée principale de l'ODD 5 – Égalité entre les sexes ?</t>
+  </si>
+  <si>
+    <t>Facile · Choix unique</t>
+  </si>
+  <si>
+    <t>Il s'applique uniquement aux gouvernements nationaux.</t>
+  </si>
+  <si>
+    <t>Ce n'est qu'un slogan marketing sans signification pratique.</t>
+  </si>
+  <si>
+    <t>Il met l'accent sur l'égalité des chances et l'autonomisation.</t>
+  </si>
+  <si>
+    <t>Il demande aux entreprises d'ignorer les impacts à long terme.</t>
+  </si>
+  <si>
+    <t>L'ODD 5 porte sur l'égalité des chances et l'autonomisation, ainsi que sur la transformation de cet objectif en actions concrètes. L'ODD 5 devient utile lorsque les personnes traduisent cet objectif général en décisions pratiques.</t>
+  </si>
+  <si>
+    <t>Pourquoi l'ODD 5 est-il pertinent pour une entreprise de distribution et de production de produits chimiques ?</t>
+  </si>
+  <si>
+    <t>Moyen · Choix unique</t>
+  </si>
+  <si>
+    <t>Parce que la durabilité n'a sa place que dans les rapports annuels.</t>
+  </si>
+  <si>
+    <t>Parce que les produits chimiques n'ont aucun lien avec la durabilité.</t>
+  </si>
+  <si>
+    <t>Parce que les ODD remplacent toutes les exigences légales.</t>
+  </si>
+  <si>
+    <t>Parce que des équipes diversifiées et des carrières équitables peuvent influencer les performances en matière de durabilité.</t>
+  </si>
+  <si>
+    <t>Les équipes diversifiées et les carrières équitables sont des domaines concrets dans lesquels une entreprise peut faire la différence. Les ODD relient les objectifs mondiaux aux choix opérationnels quotidiens.</t>
+  </si>
+  <si>
+    <t>Quelle affirmation constitue une idée fausse courante au sujet de l'ODD 5 ?</t>
+  </si>
+  <si>
+    <t>L'égalité entre les sexes signifie favoriser un groupe par rapport à un autre.</t>
+  </si>
+  <si>
+    <t>Les employés peuvent contribuer par de petites habitudes.</t>
+  </si>
+  <si>
+    <t>Les entreprises peuvent mesurer et améliorer les impacts pertinents.</t>
+  </si>
+  <si>
+    <t>L'ODD 5 peut être lié aux décisions quotidiennes.</t>
+  </si>
+  <si>
+    <t>C'est une idée fausse : elle réduit excessivement la portée de l'ODD et masque des possibilités concrètes. Une bonne question de quiz remet souvent en cause une idée reçue, car cela rend l'apprentissage mémorable.</t>
+  </si>
+  <si>
+    <t>Quel comportement permet le mieux de faire passer l'ODD 5 de la théorie à l'action ?</t>
+  </si>
+  <si>
+    <t>Parler de durabilité sans rien changer.</t>
+  </si>
+  <si>
+    <t>Choisir une amélioration concrète et la mettre en œuvre.</t>
+  </si>
+  <si>
+    <t>Attendre que quelqu'un d'autre règle tout.</t>
+  </si>
+  <si>
+    <t>Faire le contraire lorsque personne ne regarde.</t>
+  </si>
+  <si>
+    <t>Une action concrète favorise l'apprentissage et une amélioration mesurable. La sensibilisation à la durabilité doit conduire à un changement de comportement concret.</t>
+  </si>
+  <si>
+    <t>Qu'est-ce qui fait de l'ODD 5 un sujet d'apprentissage utile pour les employés ?</t>
+  </si>
+  <si>
+    <t>Il n'a aucun rapport avec la culture d'entreprise.</t>
+  </si>
+  <si>
+    <t>Il donne une réponse parfaite à chaque situation.</t>
+  </si>
+  <si>
+    <t>Il relie les défis mondiaux à des choix que les gens reconnaissent au travail et à la maison.</t>
+  </si>
+  <si>
+    <t>Il supprime le besoin de connaissances spécialisées.</t>
+  </si>
+  <si>
+    <t>L'apprentissage est le plus efficace lorsque les personnes voient le lien entre les objectifs mondiaux et des choix familiers. Les ODD sont les plus mobilisateurs lorsqu'ils paraissent pertinents, concrets et liés au rôle de chacun.</t>
+  </si>
+  <si>
+    <t>Qu'est-ce que Women@STOCKMEIER ?</t>
+  </si>
+  <si>
+    <t>Un programme de réduction pour les clients</t>
+  </si>
+  <si>
+    <t>Un système technique de stockage</t>
+  </si>
+  <si>
+    <t>Uniquement un formulaire de rapport légal</t>
+  </si>
+  <si>
+    <t>Un réseau interne soutenant le développement professionnel, les échanges et l'égalité des chances</t>
+  </si>
+  <si>
+    <t>Le rapport décrit Women@STOCKMEIER comme un réseau interne qui soutient le développement, les échanges et la visibilité des femmes. Les exemples de STOCKMEIER rendent l'ODD concret et montrent comment les initiatives du Groupe se rattachent aux objectifs mondiaux.</t>
+  </si>
+  <si>
+    <t>Selon le rapport, quelle proportion des postes de direction générale au niveau du Groupe est occupée par des femmes ?</t>
+  </si>
+  <si>
+    <t>Difficile · Choix unique</t>
+  </si>
+  <si>
+    <t>Le rapport indique que les femmes occupent 27 % des postes de direction générale. Les exemples de STOCKMEIER rendent l'ODD concret et montrent comment les initiatives du Groupe se rattachent aux objectifs mondiaux.</t>
+  </si>
+  <si>
+    <t>Quelle orientation future est mentionnée en lien avec l'égalité entre les sexes ?</t>
+  </si>
+  <si>
+    <t>Mesurer uniquement le tonnage des entrepôts</t>
+  </si>
+  <si>
+    <t>Des programmes de soutien ciblés et des parcours professionnels transparents</t>
+  </si>
+  <si>
+    <t>Supprimer toutes les formations</t>
+  </si>
+  <si>
+    <t>Éviter le développement du leadership</t>
+  </si>
+  <si>
+    <t>Le rapport mentionne des programmes de soutien ciblés, des parcours professionnels transparents et une culture d'entreprise favorable. Les exemples de STOCKMEIER rendent l'ODD concret et montrent comment les initiatives du Groupe se rattachent aux objectifs mondiaux.</t>
+  </si>
+  <si>
+    <t>À la maison ou dans la vie sociale, quelle action soutient l'ODD 5 ?</t>
+  </si>
+  <si>
+    <t>Ignorer les traitements inégaux</t>
+  </si>
+  <si>
+    <t>Répartir les tâches selon des stéréotypes</t>
+  </si>
+  <si>
+    <t>Partager équitablement les responsabilités domestiques</t>
+  </si>
+  <si>
+    <t>Décourager les personnes d'acquérir de nouvelles compétences</t>
+  </si>
+  <si>
+    <t>Le partage équitable des responsabilités favorise l'égalité des chances. Les habitudes personnelles comptent, car de nombreux petits choix deviennent significatifs lorsqu'ils sont répétés par beaucoup de personnes.</t>
+  </si>
+  <si>
+    <t>Que peut faire une personne lorsqu'elle entend un commentaire empreint de préjugés ?</t>
+  </si>
+  <si>
+    <t>Toujours garder le silence</t>
+  </si>
+  <si>
+    <t>Rire pour l'encourager</t>
+  </si>
+  <si>
+    <t>Le répéter plus fort</t>
+  </si>
+  <si>
+    <t>Le remettre en question avec respect ou poser une question réfléchie</t>
+  </si>
+  <si>
+    <t>Une réaction respectueuse peut contribuer à faire évoluer les normes quotidiennes. Les habitudes personnelles comptent, car de nombreux petits choix deviennent significatifs lorsqu'ils sont répétés par beaucoup de personnes.</t>
+  </si>
+  <si>
+    <t>Was ist der Kerngedanke von SDG 5 – Geschlechtergleichheit?</t>
+  </si>
+  <si>
+    <t>Einfach · Einfachauswahl</t>
+  </si>
+  <si>
+    <t>Es gilt nur für nationale Regierungen.</t>
+  </si>
+  <si>
+    <t>Es ist nur ein Marketingslogan ohne praktische Bedeutung.</t>
+  </si>
+  <si>
+    <t>Es konzentriert sich auf Chancengleichheit und Stärkung.</t>
+  </si>
+  <si>
+    <t>Es fordert Unternehmen auf, langfristige Auswirkungen zu ignorieren.</t>
+  </si>
+  <si>
+    <t>Bei SDG 5 geht es um Chancengleichheit und Stärkung sowie darum, dieses Ziel in konkrete Maßnahmen umzusetzen. SDG 5 wird nützlich, wenn Menschen das übergeordnete Ziel in praktische Entscheidungen übersetzen.</t>
+  </si>
+  <si>
+    <t>Warum ist SDG 5 für ein Unternehmen relevant, das Chemikalien vertreibt und produziert?</t>
+  </si>
+  <si>
+    <t>Mittel · Einfachauswahl</t>
+  </si>
+  <si>
+    <t>Weil Nachhaltigkeit nur in Geschäftsberichte gehört.</t>
+  </si>
+  <si>
+    <t>Weil Chemikalien keinen Bezug zur Nachhaltigkeit haben.</t>
+  </si>
+  <si>
+    <t>Weil die SDGs alle gesetzlichen Anforderungen ersetzen.</t>
+  </si>
+  <si>
+    <t>Weil vielfältige Teams und faire Karrierechancen die Nachhaltigkeitsleistung beeinflussen können.</t>
+  </si>
+  <si>
+    <t>Vielfältige Teams und faire Karrierechancen sind konkrete Bereiche, in denen ein Unternehmen etwas bewirken kann. Die SDGs verbinden globale Ziele mit täglichen betrieblichen Entscheidungen.</t>
+  </si>
+  <si>
+    <t>Welche Aussage ist ein häufiges Missverständnis über SDG 5?</t>
+  </si>
+  <si>
+    <t>Geschlechtergleichheit bedeutet, eine Gruppe gegenüber einer anderen zu bevorzugen.</t>
+  </si>
+  <si>
+    <t>Mitarbeitende können durch kleine Gewohnheiten beitragen.</t>
+  </si>
+  <si>
+    <t>Unternehmen können relevante Auswirkungen messen und verbessern.</t>
+  </si>
+  <si>
+    <t>SDG 5 lässt sich mit täglichen Entscheidungen verknüpfen.</t>
+  </si>
+  <si>
+    <t>Dies ist das Missverständnis: Es fasst das SDG zu eng und verdeckt praktische Chancen. Eine gute Quizfrage hinterfragt oft ein Missverständnis, weil das Gelernte dadurch besser im Gedächtnis bleibt.</t>
+  </si>
+  <si>
+    <t>Welches Verhalten setzt SDG 5 am besten von der Theorie in die Praxis um?</t>
+  </si>
+  <si>
+    <t>Über Nachhaltigkeit sprechen, aber nichts verändern.</t>
+  </si>
+  <si>
+    <t>Eine konkrete Verbesserung auswählen und konsequent umsetzen.</t>
+  </si>
+  <si>
+    <t>Warten, bis jemand anderes alles in Ordnung bringt.</t>
+  </si>
+  <si>
+    <t>Das Gegenteil tun, wenn niemand hinsieht.</t>
+  </si>
+  <si>
+    <t>Konkretes Handeln schafft Lernmöglichkeiten und messbare Verbesserungen. Nachhaltigkeitsbewusstsein sollte zu praktischen Verhaltensänderungen führen.</t>
+  </si>
+  <si>
+    <t>Was macht SDG 5 zu einem nützlichen Lernthema für Mitarbeitende?</t>
+  </si>
+  <si>
+    <t>Es hat nichts mit der Unternehmenskultur zu tun.</t>
+  </si>
+  <si>
+    <t>Es bietet für jede Situation die eine perfekte Antwort.</t>
+  </si>
+  <si>
+    <t>Es verbindet globale Herausforderungen mit Entscheidungen, die Menschen aus Beruf und Privatleben kennen.</t>
+  </si>
+  <si>
+    <t>Es macht Fachwissen überflüssig.</t>
+  </si>
+  <si>
+    <t>Am meisten lernen Menschen, wenn sie den Zusammenhang zwischen globalen Zielen und vertrauten Entscheidungen erkennen. Die SDGs sind am ansprechendsten, wenn sie relevant und konkret wirken und mit den Rollen der Menschen verbunden sind.</t>
+  </si>
+  <si>
+    <t>Was ist Women@STOCKMEIER?</t>
+  </si>
+  <si>
+    <t>Ein Kundenrabattprogramm</t>
+  </si>
+  <si>
+    <t>Ein technisches Lagersystem</t>
+  </si>
+  <si>
+    <t>Ausschließlich ein gesetzliches Berichtsformular</t>
+  </si>
+  <si>
+    <t>Ein internes Netzwerk zur Förderung von beruflicher Entwicklung, Austausch und Chancengleichheit</t>
+  </si>
+  <si>
+    <t>Der Bericht beschreibt Women@STOCKMEIER als internes Netzwerk, das die Entwicklung, den Austausch und die Sichtbarkeit von Frauen unterstützt. Die Beispiele von STOCKMEIER machen das SDG konkret und zeigen, wie Initiativen der Gruppe mit globalen Zielen verbunden sind.</t>
+  </si>
+  <si>
+    <t>Welcher Anteil der obersten Führungspositionen auf Gruppenebene wird dem Bericht zufolge von Frauen besetzt?</t>
+  </si>
+  <si>
+    <t>Schwierig · Einfachauswahl</t>
+  </si>
+  <si>
+    <t>Dem Bericht zufolge sind 27 % der obersten Führungspositionen mit Frauen besetzt. Die Beispiele von STOCKMEIER machen das SDG konkret und zeigen, wie Initiativen der Gruppe mit globalen Zielen verbunden sind.</t>
+  </si>
+  <si>
+    <t>Welcher zukünftige Schwerpunkt wird im Zusammenhang mit Geschlechtergleichheit genannt?</t>
+  </si>
+  <si>
+    <t>Nur die Lagerumschlagsmenge messen</t>
+  </si>
+  <si>
+    <t>Gezielte Förderprogramme und transparente Karrierewege</t>
+  </si>
+  <si>
+    <t>Alle Schulungen abschaffen</t>
+  </si>
+  <si>
+    <t>Führungskräfteentwicklung vermeiden</t>
+  </si>
+  <si>
+    <t>Der Bericht nennt gezielte Förderprogramme, transparente Karrierewege und eine unterstützende Unternehmenskultur. Die Beispiele von STOCKMEIER machen das SDG konkret und zeigen, wie Initiativen der Gruppe mit globalen Zielen verbunden sind.</t>
+  </si>
+  <si>
+    <t>Welche Handlung zu Hause oder im sozialen Umfeld unterstützt SDG 5?</t>
+  </si>
+  <si>
+    <t>Ungleichbehandlung ignorieren</t>
+  </si>
+  <si>
+    <t>Aufgaben aufgrund von Stereotypen verteilen</t>
+  </si>
+  <si>
+    <t>Haushaltspflichten fair aufteilen</t>
+  </si>
+  <si>
+    <t>Menschen davon abhalten, neue Fähigkeiten zu erlernen</t>
+  </si>
+  <si>
+    <t>Eine faire Aufteilung der Verantwortung unterstützt Chancengleichheit. Persönliche Gewohnheiten sind wichtig, weil viele kleine Entscheidungen bedeutsam werden, wenn sie von vielen Menschen wiederholt werden.</t>
+  </si>
+  <si>
+    <t>Was kann man tun, wenn man einen voreingenommenen Kommentar hört?</t>
+  </si>
+  <si>
+    <t>Jedes Mal schweigen</t>
+  </si>
+  <si>
+    <t>Darüber lachen und ihn dadurch bestärken</t>
+  </si>
+  <si>
+    <t>Ihn lauter wiederholen</t>
+  </si>
+  <si>
+    <t>Ihn respektvoll infrage stellen oder eine durchdachte Frage stellen</t>
+  </si>
+  <si>
+    <t>Respektvolles Hinterfragen kann dazu beitragen, alltägliche Normen zu verändern. Persönliche Gewohnheiten sind wichtig, weil viele kleine Entscheidungen bedeutsam werden, wenn sie von vielen Menschen wiederholt werden.</t>
+  </si>
+  <si>
+    <t>¿Cuál es la idea principal del ODS 5 – Igualdad de género?</t>
+  </si>
+  <si>
+    <t>Fácil · Opción única</t>
+  </si>
+  <si>
+    <t>Solo se aplica a los gobiernos nacionales.</t>
+  </si>
+  <si>
+    <t>Es solo un eslogan de marketing sin significado práctico.</t>
+  </si>
+  <si>
+    <t>Se centra en la igualdad de oportunidades y el empoderamiento.</t>
+  </si>
+  <si>
+    <t>Pide a las empresas que ignoren los impactos a largo plazo.</t>
+  </si>
+  <si>
+    <t>El ODS 5 trata sobre la igualdad de oportunidades y el empoderamiento, y sobre convertir ese objetivo en acciones prácticas. El ODS 5 resulta útil cuando las personas traducen el objetivo general en decisiones concretas.</t>
+  </si>
+  <si>
+    <t>¿Por qué es relevante el ODS 5 para una empresa de distribución y producción de productos químicos?</t>
+  </si>
+  <si>
+    <t>Medio · Opción única</t>
+  </si>
+  <si>
+    <t>Porque la sostenibilidad solo pertenece a los informes anuales.</t>
+  </si>
+  <si>
+    <t>Porque los productos químicos no tienen relación con la sostenibilidad.</t>
+  </si>
+  <si>
+    <t>Porque los ODS sustituyen todos los requisitos legales.</t>
+  </si>
+  <si>
+    <t>Porque los equipos diversos y las carreras profesionales justas pueden influir en el desempeño en materia de sostenibilidad.</t>
+  </si>
+  <si>
+    <t>Los equipos diversos y las carreras profesionales justas son ámbitos concretos en los que una empresa puede marcar la diferencia. Los ODS conectan los objetivos mundiales con las decisiones operativas diarias.</t>
+  </si>
+  <si>
+    <t>¿Qué afirmación es un malentendido común sobre el ODS 5?</t>
+  </si>
+  <si>
+    <t>La igualdad de género significa favorecer a un grupo sobre otro.</t>
+  </si>
+  <si>
+    <t>Los empleados pueden contribuir mediante pequeños hábitos.</t>
+  </si>
+  <si>
+    <t>Las empresas pueden medir y mejorar los impactos relevantes.</t>
+  </si>
+  <si>
+    <t>El ODS 5 puede vincularse a las decisiones diarias.</t>
+  </si>
+  <si>
+    <t>Este es el malentendido: limita demasiado el ODS y oculta oportunidades prácticas. Una buena pregunta de cuestionario suele cuestionar una idea errónea, porque así el aprendizaje resulta más memorable.</t>
+  </si>
+  <si>
+    <t>¿Qué comportamiento convierte mejor el ODS 5 de la teoría en acción?</t>
+  </si>
+  <si>
+    <t>Hablar de sostenibilidad sin cambiar nada.</t>
+  </si>
+  <si>
+    <t>Elegir una mejora concreta y llevarla a cabo.</t>
+  </si>
+  <si>
+    <t>Esperar a que otra persona lo solucione todo.</t>
+  </si>
+  <si>
+    <t>Hacer lo contrario cuando nadie está mirando.</t>
+  </si>
+  <si>
+    <t>La acción concreta genera aprendizaje y mejoras medibles. La concienciación sobre la sostenibilidad debe conducir a un cambio práctico de comportamiento.</t>
+  </si>
+  <si>
+    <t>¿Qué hace que el ODS 5 sea un tema de aprendizaje útil para los empleados?</t>
+  </si>
+  <si>
+    <t>No tiene relación con la cultura de la empresa.</t>
+  </si>
+  <si>
+    <t>Ofrece una respuesta perfecta para cada situación.</t>
+  </si>
+  <si>
+    <t>Relaciona los retos mundiales con decisiones que las personas reconocen en el trabajo y en casa.</t>
+  </si>
+  <si>
+    <t>Elimina la necesidad de conocimientos especializados.</t>
+  </si>
+  <si>
+    <t>El aprendizaje más eficaz se produce cuando las personas ven la relación entre los objetivos mundiales y decisiones conocidas. Los ODS resultan más atractivos cuando parecen relevantes, concretos y vinculados a las funciones de las personas.</t>
+  </si>
+  <si>
+    <t>¿Qué es Women@STOCKMEIER?</t>
+  </si>
+  <si>
+    <t>Un programa de descuentos para clientes</t>
+  </si>
+  <si>
+    <t>Un sistema técnico de almacenamiento</t>
+  </si>
+  <si>
+    <t>Únicamente un formulario de información legal</t>
+  </si>
+  <si>
+    <t>Una red interna que apoya el desarrollo profesional, el intercambio y la igualdad de oportunidades</t>
+  </si>
+  <si>
+    <t>El informe describe Women@STOCKMEIER como una red interna que apoya el desarrollo, el intercambio y la visibilidad de las mujeres. Los ejemplos de STOCKMEIER hacen que el ODS sea concreto y muestran cómo las iniciativas del Grupo se conectan con los objetivos mundiales.</t>
+  </si>
+  <si>
+    <t>Según el informe, ¿qué proporción de los puestos de alta dirección a nivel del Grupo está ocupada por mujeres?</t>
+  </si>
+  <si>
+    <t>Difícil · Opción única</t>
+  </si>
+  <si>
+    <t>El informe indica que las mujeres ocupan el 27 % de los puestos de alta dirección. Los ejemplos de STOCKMEIER hacen que el ODS sea concreto y muestran cómo las iniciativas del Grupo se conectan con los objetivos mundiales.</t>
+  </si>
+  <si>
+    <t>¿Qué enfoque futuro se menciona en relación con la igualdad de género?</t>
+  </si>
+  <si>
+    <t>Medir únicamente el tonelaje del almacén</t>
+  </si>
+  <si>
+    <t>Programas de apoyo específicos y trayectorias profesionales transparentes</t>
+  </si>
+  <si>
+    <t>Eliminar toda la formación</t>
+  </si>
+  <si>
+    <t>Evitar el desarrollo del liderazgo</t>
+  </si>
+  <si>
+    <t>El informe menciona programas de apoyo específicos, trayectorias profesionales transparentes y una cultura empresarial favorable. Los ejemplos de STOCKMEIER hacen que el ODS sea concreto y muestran cómo las iniciativas del Grupo se conectan con los objetivos mundiales.</t>
+  </si>
+  <si>
+    <t>En casa o en la vida social, ¿qué acción apoya el ODS 5?</t>
+  </si>
+  <si>
+    <t>Ignorar el trato desigual</t>
+  </si>
+  <si>
+    <t>Asignar tareas basándose en estereotipos</t>
+  </si>
+  <si>
+    <t>Compartir equitativamente las responsabilidades del hogar</t>
+  </si>
+  <si>
+    <t>Desalentar a las personas a aprender nuevas habilidades</t>
+  </si>
+  <si>
+    <t>El reparto equitativo de las responsabilidades favorece la igualdad de oportunidades. Los hábitos personales importan porque muchas pequeñas decisiones adquieren importancia cuando muchas personas las repiten.</t>
+  </si>
+  <si>
+    <t>¿Qué puede hacer una persona al oír un comentario sesgado?</t>
+  </si>
+  <si>
+    <t>Permanecer siempre en silencio</t>
+  </si>
+  <si>
+    <t>Reírse para alentarlo</t>
+  </si>
+  <si>
+    <t>Repetirlo más alto</t>
+  </si>
+  <si>
+    <t>Cuestionarlo con respeto o formular una pregunta reflexiva</t>
+  </si>
+  <si>
+    <t>Cuestionarlo con respeto puede ayudar a cambiar las normas cotidianas. Los hábitos personales importan porque muchas pequeñas decisiones adquieren importancia cuando muchas personas las repiten.</t>
+  </si>
+  <si>
+    <t>Jaka jest główna idea Celu Zrównoważonego Rozwoju 5 – Równość płci?</t>
+  </si>
+  <si>
+    <t>Łatwe · Jednokrotny wybór</t>
+  </si>
+  <si>
+    <t>Dotyczy on wyłącznie rządów krajowych.</t>
+  </si>
+  <si>
+    <t>To tylko slogan marketingowy bez praktycznego znaczenia.</t>
+  </si>
+  <si>
+    <t>Koncentruje się na równych szansach i wzmacnianiu pozycji.</t>
+  </si>
+  <si>
+    <t>Wzywa firmy do ignorowania długoterminowych skutków.</t>
+  </si>
+  <si>
+    <t>Cel 5 dotyczy równych szans i wzmacniania pozycji oraz przekładania tego celu na konkretne działania. Staje się użyteczny, gdy ludzie przekładają ogólny cel na praktyczne decyzje.</t>
+  </si>
+  <si>
+    <t>Dlaczego Cel 5 jest istotny dla firmy zajmującej się dystrybucją i produkcją chemikaliów?</t>
+  </si>
+  <si>
+    <t>Średnie · Jednokrotny wybór</t>
+  </si>
+  <si>
+    <t>Ponieważ zrównoważony rozwój powinien pojawiać się wyłącznie w raportach rocznych.</t>
+  </si>
+  <si>
+    <t>Ponieważ chemikalia nie mają związku ze zrównoważonym rozwojem.</t>
+  </si>
+  <si>
+    <t>Ponieważ Cele Zrównoważonego Rozwoju zastępują wszystkie wymogi prawne.</t>
+  </si>
+  <si>
+    <t>Ponieważ zróżnicowane zespoły i sprawiedliwe ścieżki kariery mogą wpływać na wyniki w zakresie zrównoważonego rozwoju.</t>
+  </si>
+  <si>
+    <t>Zróżnicowane zespoły i sprawiedliwe ścieżki kariery to praktyczne obszary, w których firma może coś zmienić. Cele Zrównoważonego Rozwoju łączą globalne cele z codziennymi decyzjami operacyjnymi.</t>
+  </si>
+  <si>
+    <t>Które stwierdzenie jest częstym nieporozumieniem dotyczącym Celu 5?</t>
+  </si>
+  <si>
+    <t>Równość płci oznacza faworyzowanie jednej grupy kosztem innej.</t>
+  </si>
+  <si>
+    <t>Pracownicy mogą wnosić wkład poprzez drobne codzienne nawyki.</t>
+  </si>
+  <si>
+    <t>Firmy mogą mierzyć i poprawiać istotne oddziaływania.</t>
+  </si>
+  <si>
+    <t>Cel 5 można powiązać z codziennymi decyzjami.</t>
+  </si>
+  <si>
+    <t>To błędne przekonanie: nadmiernie zawęża Cel i przesłania praktyczne możliwości. Dobre pytanie quizowe często podważa błędne przekonanie, ponieważ dzięki temu nauka lepiej zapada w pamięć.</t>
+  </si>
+  <si>
+    <t>Które zachowanie najlepiej przekłada Cel 5 z teorii na działanie?</t>
+  </si>
+  <si>
+    <t>Mówienie o zrównoważonym rozwoju bez wprowadzania zmian.</t>
+  </si>
+  <si>
+    <t>Wybranie konkretnego usprawnienia i konsekwentne jego wdrożenie.</t>
+  </si>
+  <si>
+    <t>Czekanie, aż ktoś inny wszystko naprawi.</t>
+  </si>
+  <si>
+    <t>Postępowanie odwrotnie, gdy nikt nie patrzy.</t>
+  </si>
+  <si>
+    <t>Konkretne działanie sprzyja uczeniu się i wymiernej poprawie. Świadomość zrównoważonego rozwoju powinna prowadzić do praktycznej zmiany zachowania.</t>
+  </si>
+  <si>
+    <t>Co sprawia, że Cel 5 jest wartościowym tematem edukacyjnym dla pracowników?</t>
+  </si>
+  <si>
+    <t>Nie ma związku z kulturą firmy.</t>
+  </si>
+  <si>
+    <t>Daje jedną idealną odpowiedź w każdej sytuacji.</t>
+  </si>
+  <si>
+    <t>Łączy globalne wyzwania z wyborami znanymi ludziom z pracy i domu.</t>
+  </si>
+  <si>
+    <t>Eliminuje potrzebę wiedzy eksperckiej.</t>
+  </si>
+  <si>
+    <t>Najskuteczniejsza nauka ma miejsce wtedy, gdy ludzie dostrzegają związek między globalnymi celami a znanymi wyborami. Cele Zrównoważonego Rozwoju są najbardziej angażujące, gdy są istotne, konkretne i powiązane z rolami ludzi.</t>
+  </si>
+  <si>
+    <t>Czym jest Women@STOCKMEIER?</t>
+  </si>
+  <si>
+    <t>Program rabatowy dla klientów</t>
+  </si>
+  <si>
+    <t>Techniczny system magazynowy</t>
+  </si>
+  <si>
+    <t>Wyłącznie formularz sprawozdawczości prawnej</t>
+  </si>
+  <si>
+    <t>Wewnętrzna sieć wspierająca rozwój zawodowy, wymianę doświadczeń i równe szanse</t>
+  </si>
+  <si>
+    <t>Raport opisuje Women@STOCKMEIER jako wewnętrzną sieć wspierającą rozwój, wymianę doświadczeń i widoczność kobiet. Przykłady STOCKMEIER konkretyzują Cel i pokazują, jak inicjatywy Grupy łączą się z globalnymi celami.</t>
+  </si>
+  <si>
+    <t>Jaki odsetek stanowisk najwyższego szczebla zarządzania na poziomie Grupy zajmują według raportu kobiety?</t>
+  </si>
+  <si>
+    <t>Trudne · Jednokrotny wybór</t>
+  </si>
+  <si>
+    <t>Raport podaje, że kobiety zajmują 27% stanowisk najwyższego szczebla zarządzania. Przykłady STOCKMEIER konkretyzują Cel i pokazują, jak inicjatywy Grupy łączą się z globalnymi celami.</t>
+  </si>
+  <si>
+    <t>Jaki przyszły kierunek działań wspomniano w kontekście równości płci?</t>
+  </si>
+  <si>
+    <t>Wyłącznie pomiar tonażu magazynowego</t>
+  </si>
+  <si>
+    <t>Ukierunkowane programy wsparcia i przejrzyste ścieżki kariery</t>
+  </si>
+  <si>
+    <t>Likwidacja wszystkich szkoleń</t>
+  </si>
+  <si>
+    <t>Unikanie rozwoju przywództwa</t>
+  </si>
+  <si>
+    <t>Raport wymienia ukierunkowane programy wsparcia, przejrzyste ścieżki kariery i wspierającą kulturę organizacyjną. Przykłady STOCKMEIER konkretyzują Cel i pokazują, jak inicjatywy Grupy łączą się z globalnymi celami.</t>
+  </si>
+  <si>
+    <t>Które działanie w domu lub w życiu społecznym wspiera Cel 5?</t>
+  </si>
+  <si>
+    <t>Ignorowanie nierównego traktowania</t>
+  </si>
+  <si>
+    <t>Przydzielanie zadań na podstawie stereotypów</t>
+  </si>
+  <si>
+    <t>Sprawiedliwy podział obowiązków domowych</t>
+  </si>
+  <si>
+    <t>Zniechęcanie ludzi do zdobywania nowych umiejętności</t>
+  </si>
+  <si>
+    <t>Sprawiedliwy podział obowiązków wspiera równe szanse. Osobiste nawyki mają znaczenie, ponieważ wiele drobnych wyborów nabiera wagi, gdy są powtarzane przez wiele osób.</t>
+  </si>
+  <si>
+    <t>Co można zrobić, słysząc stronniczy komentarz?</t>
+  </si>
+  <si>
+    <t>Za każdym razem milczeć</t>
+  </si>
+  <si>
+    <t>Śmiać się, aby go zachęcić</t>
+  </si>
+  <si>
+    <t>Powtórzyć go głośniej</t>
+  </si>
+  <si>
+    <t>Zareagować z szacunkiem lub zadać przemyślane pytanie</t>
+  </si>
+  <si>
+    <t>Pełna szacunku reakcja może pomóc zmieniać codzienne normy. Osobiste nawyki mają znaczenie, ponieważ wiele drobnych wyborów nabiera wagi, gdy są powtarzane przez wiele osób.</t>
+  </si>
+  <si>
+    <t>Qual è l'idea principale dell'OSS 5 – Parità di genere?</t>
+  </si>
+  <si>
+    <t>Facile · Scelta singola</t>
+  </si>
+  <si>
+    <t>Si applica solo ai governi nazionali.</t>
+  </si>
+  <si>
+    <t>È solo uno slogan di marketing privo di significato pratico.</t>
+  </si>
+  <si>
+    <t>Si concentra sulle pari opportunità e sull'emancipazione.</t>
+  </si>
+  <si>
+    <t>Chiede alle aziende di ignorare gli impatti a lungo termine.</t>
+  </si>
+  <si>
+    <t>L'OSS 5 riguarda le pari opportunità e l'emancipazione, nonché la trasformazione di questo obiettivo in azioni concrete. L'OSS 5 diventa utile quando le persone traducono l'obiettivo generale in decisioni pratiche.</t>
+  </si>
+  <si>
+    <t>Perché l'OSS 5 è rilevante per un'azienda che distribuisce e produce prodotti chimici?</t>
+  </si>
+  <si>
+    <t>Medio · Scelta singola</t>
+  </si>
+  <si>
+    <t>Perché la sostenibilità appartiene solo alle relazioni annuali.</t>
+  </si>
+  <si>
+    <t>Perché i prodotti chimici non hanno alcun legame con la sostenibilità.</t>
+  </si>
+  <si>
+    <t>Perché gli OSS sostituiscono tutti i requisiti di legge.</t>
+  </si>
+  <si>
+    <t>Perché team diversificati e percorsi di carriera equi possono influenzare le prestazioni di sostenibilità.</t>
+  </si>
+  <si>
+    <t>Team diversificati e percorsi di carriera equi sono ambiti concreti in cui un'azienda può fare la differenza. Gli OSS collegano gli obiettivi globali alle scelte operative quotidiane.</t>
+  </si>
+  <si>
+    <t>Quale affermazione rappresenta un malinteso comune sull'OSS 5?</t>
+  </si>
+  <si>
+    <t>La parità di genere significa favorire un gruppo rispetto a un altro.</t>
+  </si>
+  <si>
+    <t>I dipendenti possono contribuire attraverso piccole abitudini.</t>
+  </si>
+  <si>
+    <t>Le aziende possono misurare e migliorare gli impatti rilevanti.</t>
+  </si>
+  <si>
+    <t>L'OSS 5 può essere collegato alle decisioni quotidiane.</t>
+  </si>
+  <si>
+    <t>Questo è il malinteso: restringe troppo l'OSS e nasconde opportunità concrete. Una buona domanda di un quiz spesso mette in discussione un'idea errata, perché così l'apprendimento resta più impresso.</t>
+  </si>
+  <si>
+    <t>Quale comportamento traduce meglio l'OSS 5 dalla teoria all'azione?</t>
+  </si>
+  <si>
+    <t>Parlare di sostenibilità senza cambiare nulla.</t>
+  </si>
+  <si>
+    <t>Scegliere un miglioramento concreto e portarlo a termine.</t>
+  </si>
+  <si>
+    <t>Aspettare che qualcun altro risolva tutto.</t>
+  </si>
+  <si>
+    <t>Fare il contrario quando nessuno controlla.</t>
+  </si>
+  <si>
+    <t>L'azione concreta genera apprendimento e miglioramenti misurabili. La consapevolezza della sostenibilità dovrebbe portare a un cambiamento pratico dei comportamenti.</t>
+  </si>
+  <si>
+    <t>Che cosa rende l'OSS 5 un tema formativo utile per i dipendenti?</t>
+  </si>
+  <si>
+    <t>Non ha alcun rapporto con la cultura aziendale.</t>
+  </si>
+  <si>
+    <t>Offre una risposta perfetta per ogni situazione.</t>
+  </si>
+  <si>
+    <t>Collega le sfide globali a scelte che le persone riconoscono sul lavoro e a casa.</t>
+  </si>
+  <si>
+    <t>Elimina la necessità di conoscenze specialistiche.</t>
+  </si>
+  <si>
+    <t>L'apprendimento è più efficace quando le persone vedono il legame tra obiettivi globali e scelte familiari. Gli OSS sono più coinvolgenti quando appaiono pertinenti, concreti e collegati ai ruoli delle persone.</t>
+  </si>
+  <si>
+    <t>Che cos'è Women@STOCKMEIER?</t>
+  </si>
+  <si>
+    <t>Un programma di sconti per i clienti</t>
+  </si>
+  <si>
+    <t>Un sistema tecnico di stoccaggio</t>
+  </si>
+  <si>
+    <t>Esclusivamente un modulo di rendicontazione legale</t>
+  </si>
+  <si>
+    <t>Una rete interna che sostiene lo sviluppo professionale, lo scambio e le pari opportunità</t>
+  </si>
+  <si>
+    <t>Il rapporto descrive Women@STOCKMEIER come una rete interna che sostiene lo sviluppo, lo scambio e la visibilità delle donne. Gli esempi di STOCKMEIER rendono concreto l'OSS e mostrano come le iniziative del Gruppo si colleghino agli obiettivi globali.</t>
+  </si>
+  <si>
+    <t>Secondo il rapporto, quale percentuale delle posizioni di alta dirigenza a livello di Gruppo è occupata da donne?</t>
+  </si>
+  <si>
+    <t>Difficile · Scelta singola</t>
+  </si>
+  <si>
+    <t>Il rapporto afferma che le donne occupano il 27% delle posizioni di alta dirigenza. Gli esempi di STOCKMEIER rendono concreto l'OSS e mostrano come le iniziative del Gruppo si colleghino agli obiettivi globali.</t>
+  </si>
+  <si>
+    <t>Quale obiettivo futuro viene menzionato in relazione alla parità di genere?</t>
+  </si>
+  <si>
+    <t>Misurare soltanto il tonnellaggio del magazzino</t>
+  </si>
+  <si>
+    <t>Programmi di sostegno mirati e percorsi di carriera trasparenti</t>
+  </si>
+  <si>
+    <t>Eliminare tutta la formazione</t>
+  </si>
+  <si>
+    <t>Evitare lo sviluppo della leadership</t>
+  </si>
+  <si>
+    <t>Il rapporto menziona programmi di sostegno mirati, percorsi di carriera trasparenti e una cultura aziendale favorevole. Gli esempi di STOCKMEIER rendono concreto l'OSS e mostrano come le iniziative del Gruppo si colleghino agli obiettivi globali.</t>
+  </si>
+  <si>
+    <t>A casa o nella vita sociale, quale azione sostiene l'OSS 5?</t>
+  </si>
+  <si>
+    <t>Ignorare i trattamenti iniqui</t>
+  </si>
+  <si>
+    <t>Assegnare i compiti in base agli stereotipi</t>
+  </si>
+  <si>
+    <t>Condividere equamente le responsabilità domestiche</t>
+  </si>
+  <si>
+    <t>Scoraggiare le persone dall'apprendere nuove competenze</t>
+  </si>
+  <si>
+    <t>La condivisione equa delle responsabilità sostiene le pari opportunità. Le abitudini personali contano, perché molte piccole scelte diventano significative quando vengono ripetute da molte persone.</t>
+  </si>
+  <si>
+    <t>Che cosa può fare una persona quando sente un commento prevenuto?</t>
+  </si>
+  <si>
+    <t>Rimanere sempre in silenzio</t>
+  </si>
+  <si>
+    <t>Ridere per incoraggiarlo</t>
+  </si>
+  <si>
+    <t>Ripeterlo più forte</t>
+  </si>
+  <si>
+    <t>Contestarlo con rispetto o porre una domanda ponderata</t>
+  </si>
+  <si>
+    <t>Una reazione rispettosa può contribuire a cambiare le norme quotidiane. Le abitudini personali contano, perché molte piccole scelte diventano significative quando vengono ripetute da molte persone.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -314,7 +1387,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -328,11 +1401,237 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Standaard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="72">
+    <dxf>
+      <alignment vertical="top" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -343,6 +1642,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -359,6 +1662,120 @@
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="correct"/>
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="explanation"/>
     <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Comments ZF"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{9DF42BEE-242B-4AA2-9D85-23FCDFA74B9F}" name="Questions_NL" displayName="Questions_NL" ref="A1:J11" totalsRowShown="0" headerRowDxfId="70" dataDxfId="69">
+  <autoFilter ref="A1:J11" xr:uid="{9DF42BEE-242B-4AA2-9D85-23FCDFA74B9F}"/>
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{D45A8481-EEF8-47C4-924C-2DB2C1781432}" name="type" dataDxfId="71"/>
+    <tableColumn id="2" xr3:uid="{A4872670-0399-43B8-B680-2B5D56ECCB06}" name="question" dataDxfId="68"/>
+    <tableColumn id="3" xr3:uid="{705EDBE4-2F08-4E86-8E9F-72702575CC26}" name="note" dataDxfId="67"/>
+    <tableColumn id="4" xr3:uid="{A46A35BD-7672-4D9C-BA51-A4BD9FBFBD54}" name="option1" dataDxfId="66"/>
+    <tableColumn id="5" xr3:uid="{F99E3940-DFE8-4655-BC2C-2D4D9B906B35}" name="option2" dataDxfId="65"/>
+    <tableColumn id="6" xr3:uid="{C2FD20CD-EF6C-4098-8754-B8D93C411FA9}" name="option3" dataDxfId="64"/>
+    <tableColumn id="7" xr3:uid="{23721200-F1F2-436F-9EB0-0BF482E33DB0}" name="option4" dataDxfId="63"/>
+    <tableColumn id="8" xr3:uid="{AA152B03-C19B-453E-84A8-4ED8310221B7}" name="correct" dataDxfId="62"/>
+    <tableColumn id="9" xr3:uid="{B2400089-8536-4464-925E-28427C3B7301}" name="explanation" dataDxfId="61"/>
+    <tableColumn id="10" xr3:uid="{9387DAC4-A5AE-4147-8E53-3490D265AA96}" name="Comments ZF" dataDxfId="60"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{F2ED995B-AA99-481E-B3BF-8A00B2053E27}" name="Questions_FR" displayName="Questions_FR" ref="A1:J11" totalsRowShown="0" headerRowDxfId="58" dataDxfId="57">
+  <autoFilter ref="A1:J11" xr:uid="{F2ED995B-AA99-481E-B3BF-8A00B2053E27}"/>
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{85D41F39-8852-4C37-9035-EA43B87AEF10}" name="type" dataDxfId="59"/>
+    <tableColumn id="2" xr3:uid="{95D38A4F-61BB-4786-B304-53CC4044F560}" name="question" dataDxfId="56"/>
+    <tableColumn id="3" xr3:uid="{AA637EEE-1B22-4428-B1DB-5017D2D1F7BF}" name="note" dataDxfId="55"/>
+    <tableColumn id="4" xr3:uid="{241C73E6-73B1-4D2D-8A82-F1CC4112ECCD}" name="option1" dataDxfId="54"/>
+    <tableColumn id="5" xr3:uid="{3601AE46-9395-4363-A690-56C6A7BE8354}" name="option2" dataDxfId="53"/>
+    <tableColumn id="6" xr3:uid="{CF843634-F3BF-4443-8901-9796647B7294}" name="option3" dataDxfId="52"/>
+    <tableColumn id="7" xr3:uid="{F6EB5583-9DAE-4971-AD7C-17D07810DEB1}" name="option4" dataDxfId="51"/>
+    <tableColumn id="8" xr3:uid="{146636A3-FEA0-44AC-A316-288FA18FC324}" name="correct" dataDxfId="50"/>
+    <tableColumn id="9" xr3:uid="{07C5461E-0D47-46B9-A81F-1943DF43EBC1}" name="explanation" dataDxfId="49"/>
+    <tableColumn id="10" xr3:uid="{55E678C3-E1BE-4D39-836D-739F7A49ADF3}" name="Comments ZF" dataDxfId="48"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{D5E4ADC6-9623-478F-8965-FE8C1872D69B}" name="Questions_GE" displayName="Questions_GE" ref="A1:J11" totalsRowShown="0" headerRowDxfId="46" dataDxfId="45">
+  <autoFilter ref="A1:J11" xr:uid="{D5E4ADC6-9623-478F-8965-FE8C1872D69B}"/>
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{A5B906DB-536D-462E-8315-EB8A94BECEB3}" name="type" dataDxfId="47"/>
+    <tableColumn id="2" xr3:uid="{689B2EB8-E9C1-44F0-9B3F-4B973A78393A}" name="question" dataDxfId="44"/>
+    <tableColumn id="3" xr3:uid="{FC6E3E1C-9C7B-4461-BD6D-21308243CE20}" name="note" dataDxfId="43"/>
+    <tableColumn id="4" xr3:uid="{13244CBC-1111-4705-B512-522F09EA34CA}" name="option1" dataDxfId="42"/>
+    <tableColumn id="5" xr3:uid="{A42F60E8-9E8E-494A-96D1-D90EC7FFE833}" name="option2" dataDxfId="41"/>
+    <tableColumn id="6" xr3:uid="{1D858B1A-513E-4C48-8918-E26051537FF9}" name="option3" dataDxfId="40"/>
+    <tableColumn id="7" xr3:uid="{91C98519-265C-497B-99F0-F1D949994458}" name="option4" dataDxfId="39"/>
+    <tableColumn id="8" xr3:uid="{0C6DAD16-2FAC-4020-9D5D-4349BEF5EDE9}" name="correct" dataDxfId="38"/>
+    <tableColumn id="9" xr3:uid="{D3DD0ADE-26F9-4057-BA91-76E032F91241}" name="explanation" dataDxfId="37"/>
+    <tableColumn id="10" xr3:uid="{377ECB20-A1DB-4830-9DE0-03622BDA3CF9}" name="Comments ZF" dataDxfId="36"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{B0A753DB-4CBB-4621-8D6B-D007D6808A3A}" name="Questions_SP" displayName="Questions_SP" ref="A1:J11" totalsRowShown="0" headerRowDxfId="34" dataDxfId="33">
+  <autoFilter ref="A1:J11" xr:uid="{B0A753DB-4CBB-4621-8D6B-D007D6808A3A}"/>
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{3C5C0575-720D-4FC8-93E1-C160993E213C}" name="type" dataDxfId="35"/>
+    <tableColumn id="2" xr3:uid="{1F5644AE-0038-4C8B-BB81-FBE6555A1FB5}" name="question" dataDxfId="32"/>
+    <tableColumn id="3" xr3:uid="{B8C3002A-5D12-4DA0-B7F8-1007F734AC8F}" name="note" dataDxfId="31"/>
+    <tableColumn id="4" xr3:uid="{70855D99-4700-4CC0-9A89-3BEB25099D93}" name="option1" dataDxfId="30"/>
+    <tableColumn id="5" xr3:uid="{AC792FCB-C409-4C1C-8004-4E691D9D7773}" name="option2" dataDxfId="29"/>
+    <tableColumn id="6" xr3:uid="{E6E2EBCF-7622-401D-9974-013CB7869641}" name="option3" dataDxfId="28"/>
+    <tableColumn id="7" xr3:uid="{2A10B952-34F0-4231-8D12-D1B80C9C4389}" name="option4" dataDxfId="27"/>
+    <tableColumn id="8" xr3:uid="{89744816-038C-4E12-A6F5-8E4E275F23E2}" name="correct" dataDxfId="26"/>
+    <tableColumn id="9" xr3:uid="{80EA07A1-ED40-4114-BF36-62AA6D486FA3}" name="explanation" dataDxfId="25"/>
+    <tableColumn id="10" xr3:uid="{4D208383-95AB-42DD-98EE-9F546EEDBF15}" name="Comments ZF" dataDxfId="24"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{3467AE70-DCBA-4CA8-92DA-AE94E6D8E2FB}" name="Questions_IT" displayName="Questions_IT" ref="A1:J11" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9">
+  <autoFilter ref="A1:J11" xr:uid="{3467AE70-DCBA-4CA8-92DA-AE94E6D8E2FB}"/>
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{84AA4B6E-1865-437C-8A97-E4247246F125}" name="type" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{8ED6F6B6-3741-45FA-955D-D4F1AC8339F8}" name="question" dataDxfId="8"/>
+    <tableColumn id="3" xr3:uid="{B0A63E07-BCA3-4239-8145-5C7025222A19}" name="note" dataDxfId="7"/>
+    <tableColumn id="4" xr3:uid="{9ABDFA4F-A47F-423E-BA24-58267B5EC6FA}" name="option1" dataDxfId="6"/>
+    <tableColumn id="5" xr3:uid="{B499B3BF-8C90-4CBB-A9E8-84BCA2920B73}" name="option2" dataDxfId="5"/>
+    <tableColumn id="6" xr3:uid="{D1F6C702-B5FE-43FD-9163-2D2858F8EAF4}" name="option3" dataDxfId="4"/>
+    <tableColumn id="7" xr3:uid="{755498C9-DABA-4942-824C-DA93EDF118A8}" name="option4" dataDxfId="3"/>
+    <tableColumn id="8" xr3:uid="{9DD5C79F-A749-41E2-820B-3D68DC0EECCA}" name="correct" dataDxfId="2"/>
+    <tableColumn id="9" xr3:uid="{A9265DAD-EC97-46D4-A313-3893EAC1EE6F}" name="explanation" dataDxfId="1"/>
+    <tableColumn id="10" xr3:uid="{DC4A3A40-1903-483B-8914-DCE1D80F404C}" name="Comments ZF" dataDxfId="0"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{A2943D30-E5EC-4925-990C-8582C33FF7A3}" name="Questions_PL" displayName="Questions_PL" ref="A1:J11" totalsRowShown="0" headerRowDxfId="22" dataDxfId="21">
+  <autoFilter ref="A1:J11" xr:uid="{A2943D30-E5EC-4925-990C-8582C33FF7A3}"/>
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{EBC59FD2-8DE8-4241-A856-B1E3DF9D76DC}" name="type" dataDxfId="23"/>
+    <tableColumn id="2" xr3:uid="{18008FF2-CF77-4A03-8E1E-551E6AF5E340}" name="question" dataDxfId="20"/>
+    <tableColumn id="3" xr3:uid="{CD9B7C72-7E07-44AD-876C-227130539BE5}" name="note" dataDxfId="19"/>
+    <tableColumn id="4" xr3:uid="{C29A3DA4-F9DB-42EC-9483-9D05FA6EC954}" name="option1" dataDxfId="18"/>
+    <tableColumn id="5" xr3:uid="{8ABB5CD8-B85F-483A-BC64-5FA675C2C743}" name="option2" dataDxfId="17"/>
+    <tableColumn id="6" xr3:uid="{26CC17F2-67F6-4542-8B79-8B6E7DAEF829}" name="option3" dataDxfId="16"/>
+    <tableColumn id="7" xr3:uid="{92CEB64B-A8DC-46A4-BA29-31CAC0384117}" name="option4" dataDxfId="15"/>
+    <tableColumn id="8" xr3:uid="{920A0E79-5515-4F74-BCC9-7E5FA4019930}" name="correct" dataDxfId="14"/>
+    <tableColumn id="9" xr3:uid="{5306BDAC-35E4-4523-B9CA-22AE7AD0C5A5}" name="explanation" dataDxfId="13"/>
+    <tableColumn id="10" xr3:uid="{472C526E-A9B5-4DDF-B3EC-AC048A606315}" name="Comments ZF" dataDxfId="12"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -650,7 +2067,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="55" customWidth="1"/>
@@ -661,7 +2078,7 @@
     <col min="10" max="10" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="24" customHeight="1">
+    <row r="1" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -693,7 +2110,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="72" customHeight="1">
+    <row r="2" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
@@ -723,7 +2140,7 @@
       </c>
       <c r="J2" s="2"/>
     </row>
-    <row r="3" spans="1:10" ht="72" customHeight="1">
+    <row r="3" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
@@ -753,7 +2170,7 @@
       </c>
       <c r="J3" s="2"/>
     </row>
-    <row r="4" spans="1:10" ht="72" customHeight="1">
+    <row r="4" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
@@ -783,7 +2200,7 @@
       </c>
       <c r="J4" s="2"/>
     </row>
-    <row r="5" spans="1:10" ht="72" customHeight="1">
+    <row r="5" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
@@ -813,7 +2230,7 @@
       </c>
       <c r="J5" s="2"/>
     </row>
-    <row r="6" spans="1:10" ht="72" customHeight="1">
+    <row r="6" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
@@ -843,7 +2260,7 @@
       </c>
       <c r="J6" s="2"/>
     </row>
-    <row r="7" spans="1:10" ht="72" customHeight="1">
+    <row r="7" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>10</v>
       </c>
@@ -873,7 +2290,7 @@
       </c>
       <c r="J7" s="2"/>
     </row>
-    <row r="8" spans="1:10" ht="72" customHeight="1">
+    <row r="8" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>10</v>
       </c>
@@ -903,7 +2320,7 @@
       </c>
       <c r="J8" s="2"/>
     </row>
-    <row r="9" spans="1:10" ht="72" customHeight="1">
+    <row r="9" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>10</v>
       </c>
@@ -933,7 +2350,7 @@
       </c>
       <c r="J9" s="2"/>
     </row>
-    <row r="10" spans="1:10" ht="72" customHeight="1">
+    <row r="10" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>10</v>
       </c>
@@ -963,7 +2380,7 @@
       </c>
       <c r="J10" s="2"/>
     </row>
-    <row r="11" spans="1:10" ht="72" customHeight="1">
+    <row r="11" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
@@ -1001,26 +2418,2131 @@
 </worksheet>
 </file>
 
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2aad7df3-4ab7-4daa-980d-cf7206357ce9">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{868F196C-5735-43D6-BE37-C6FBA028DEAE}">
+  <dimension ref="A1:J11"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="11.81640625" customWidth="1"/>
+    <col min="2" max="2" width="45.453125" style="7" customWidth="1"/>
+    <col min="3" max="3" width="21.81640625" style="7" customWidth="1"/>
+    <col min="4" max="7" width="34.54296875" style="7" customWidth="1"/>
+    <col min="8" max="8" width="10.90625" style="7" customWidth="1"/>
+    <col min="9" max="9" width="61.81640625" style="7" customWidth="1"/>
+    <col min="10" max="10" width="18.1796875" style="7" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="H2" s="2">
+        <v>3</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="J2" s="2"/>
+    </row>
+    <row r="3" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A3" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H3" s="2">
+        <v>4</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="J3" s="2"/>
+    </row>
+    <row r="4" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A4" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H4" s="2">
+        <v>1</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="J4" s="2"/>
+    </row>
+    <row r="5" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+      <c r="A5" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="H5" s="2">
+        <v>2</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="J5" s="2"/>
+    </row>
+    <row r="6" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A6" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="H6" s="2">
+        <v>3</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="J6" s="2"/>
+    </row>
+    <row r="7" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A7" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="H7" s="2">
+        <v>4</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="J7" s="2"/>
+    </row>
+    <row r="8" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A8" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="D8" s="6">
+        <v>0.27</v>
+      </c>
+      <c r="E8" s="6">
+        <v>1</v>
+      </c>
+      <c r="F8" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="G8" s="6">
+        <v>0</v>
+      </c>
+      <c r="H8" s="2">
+        <v>1</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="J8" s="2"/>
+    </row>
+    <row r="9" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A9" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="H9" s="2">
+        <v>2</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="J9" s="2"/>
+    </row>
+    <row r="10" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A10" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="H10" s="2">
+        <v>3</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="J10" s="2"/>
+    </row>
+    <row r="11" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A11" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="H11" s="2">
+        <v>4</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="J11" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{872F2D3A-60B2-4AA1-8867-348D6416FE4F}">
+  <dimension ref="A1:J11"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="11.81640625" customWidth="1"/>
+    <col min="2" max="2" width="45.453125" style="7" customWidth="1"/>
+    <col min="3" max="3" width="21.81640625" style="7" customWidth="1"/>
+    <col min="4" max="7" width="34.54296875" style="7" customWidth="1"/>
+    <col min="8" max="8" width="10.90625" style="7" customWidth="1"/>
+    <col min="9" max="9" width="61.81640625" style="7" customWidth="1"/>
+    <col min="10" max="10" width="18.1796875" style="7" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A2" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="H2" s="2">
+        <v>3</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="J2" s="2"/>
+    </row>
+    <row r="3" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A3" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="H3" s="2">
+        <v>4</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="J3" s="2"/>
+    </row>
+    <row r="4" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A4" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="H4" s="2">
+        <v>1</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="J4" s="2"/>
+    </row>
+    <row r="5" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="H5" s="2">
+        <v>2</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="J5" s="2"/>
+    </row>
+    <row r="6" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A6" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="H6" s="2">
+        <v>3</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="J6" s="2"/>
+    </row>
+    <row r="7" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A7" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="H7" s="2">
+        <v>4</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="J7" s="2"/>
+    </row>
+    <row r="8" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A8" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="D8" s="6">
+        <v>0.27</v>
+      </c>
+      <c r="E8" s="6">
+        <v>1</v>
+      </c>
+      <c r="F8" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="G8" s="6">
+        <v>0</v>
+      </c>
+      <c r="H8" s="2">
+        <v>1</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="J8" s="2"/>
+    </row>
+    <row r="9" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A9" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="H9" s="2">
+        <v>2</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="J9" s="2"/>
+    </row>
+    <row r="10" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A10" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="H10" s="2">
+        <v>3</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="J10" s="2"/>
+    </row>
+    <row r="11" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A11" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="H11" s="2">
+        <v>4</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="J11" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA27AA3A-9137-4728-A83D-07B1E39090B9}">
+  <dimension ref="A1:J11"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="11.81640625" customWidth="1"/>
+    <col min="2" max="2" width="45.453125" style="7" customWidth="1"/>
+    <col min="3" max="3" width="21.81640625" style="7" customWidth="1"/>
+    <col min="4" max="7" width="34.54296875" style="7" customWidth="1"/>
+    <col min="8" max="8" width="10.90625" style="7" customWidth="1"/>
+    <col min="9" max="9" width="61.81640625" style="7" customWidth="1"/>
+    <col min="10" max="10" width="18.1796875" style="7" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A2" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="H2" s="2">
+        <v>3</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="J2" s="2"/>
+    </row>
+    <row r="3" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A3" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="H3" s="2">
+        <v>4</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="J3" s="2"/>
+    </row>
+    <row r="4" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A4" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="H4" s="2">
+        <v>1</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="J4" s="2"/>
+    </row>
+    <row r="5" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="H5" s="2">
+        <v>2</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="J5" s="2"/>
+    </row>
+    <row r="6" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A6" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="H6" s="2">
+        <v>3</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="J6" s="2"/>
+    </row>
+    <row r="7" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A7" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="H7" s="2">
+        <v>4</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="J7" s="2"/>
+    </row>
+    <row r="8" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A8" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="D8" s="6">
+        <v>0.27</v>
+      </c>
+      <c r="E8" s="6">
+        <v>1</v>
+      </c>
+      <c r="F8" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="G8" s="6">
+        <v>0</v>
+      </c>
+      <c r="H8" s="2">
+        <v>1</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="J8" s="2"/>
+    </row>
+    <row r="9" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A9" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="H9" s="2">
+        <v>2</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="J9" s="2"/>
+    </row>
+    <row r="10" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A10" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="H10" s="2">
+        <v>3</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="J10" s="2"/>
+    </row>
+    <row r="11" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A11" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="H11" s="2">
+        <v>4</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="J11" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A0C0852-8CD5-4131-989D-FF56BF2BC9CD}">
+  <dimension ref="A1:J11"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="11.81640625" customWidth="1"/>
+    <col min="2" max="2" width="45.453125" style="7" customWidth="1"/>
+    <col min="3" max="3" width="21.81640625" style="7" customWidth="1"/>
+    <col min="4" max="7" width="34.54296875" style="7" customWidth="1"/>
+    <col min="8" max="8" width="10.90625" style="7" customWidth="1"/>
+    <col min="9" max="9" width="61.81640625" style="7" customWidth="1"/>
+    <col min="10" max="10" width="18.1796875" style="7" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A2" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="H2" s="2">
+        <v>3</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="J2" s="2"/>
+    </row>
+    <row r="3" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A3" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="H3" s="2">
+        <v>4</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="J3" s="2"/>
+    </row>
+    <row r="4" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A4" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="H4" s="2">
+        <v>1</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="J4" s="2"/>
+    </row>
+    <row r="5" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="H5" s="2">
+        <v>2</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="J5" s="2"/>
+    </row>
+    <row r="6" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A6" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="H6" s="2">
+        <v>3</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="J6" s="2"/>
+    </row>
+    <row r="7" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A7" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="H7" s="2">
+        <v>4</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="J7" s="2"/>
+    </row>
+    <row r="8" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A8" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="D8" s="6">
+        <v>0.27</v>
+      </c>
+      <c r="E8" s="6">
+        <v>1</v>
+      </c>
+      <c r="F8" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="G8" s="6">
+        <v>0</v>
+      </c>
+      <c r="H8" s="2">
+        <v>1</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="J8" s="2"/>
+    </row>
+    <row r="9" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A9" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="H9" s="2">
+        <v>2</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="J9" s="2"/>
+    </row>
+    <row r="10" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A10" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="H10" s="2">
+        <v>3</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="J10" s="2"/>
+    </row>
+    <row r="11" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A11" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="H11" s="2">
+        <v>4</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="J11" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DE9C0A2-B94F-4B6C-B1C9-CED6107DE310}">
+  <dimension ref="A1:J11"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="11.81640625" customWidth="1"/>
+    <col min="2" max="2" width="45.453125" style="7" customWidth="1"/>
+    <col min="3" max="3" width="21.81640625" style="7" customWidth="1"/>
+    <col min="4" max="7" width="34.54296875" style="7" customWidth="1"/>
+    <col min="8" max="8" width="10.90625" style="7" customWidth="1"/>
+    <col min="9" max="9" width="61.81640625" style="7" customWidth="1"/>
+    <col min="10" max="10" width="18.1796875" style="7" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A2" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="H2" s="2">
+        <v>3</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="J2" s="2"/>
+    </row>
+    <row r="3" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A3" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="H3" s="2">
+        <v>4</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="J3" s="2"/>
+    </row>
+    <row r="4" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A4" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="H4" s="2">
+        <v>1</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="J4" s="2"/>
+    </row>
+    <row r="5" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="H5" s="2">
+        <v>2</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="J5" s="2"/>
+    </row>
+    <row r="6" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A6" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="H6" s="2">
+        <v>3</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="J6" s="2"/>
+    </row>
+    <row r="7" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A7" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="H7" s="2">
+        <v>4</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="J7" s="2"/>
+    </row>
+    <row r="8" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A8" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="D8" s="6">
+        <v>0.27</v>
+      </c>
+      <c r="E8" s="6">
+        <v>1</v>
+      </c>
+      <c r="F8" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="G8" s="6">
+        <v>0</v>
+      </c>
+      <c r="H8" s="2">
+        <v>1</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="J8" s="2"/>
+    </row>
+    <row r="9" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A9" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="H9" s="2">
+        <v>2</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="J9" s="2"/>
+    </row>
+    <row r="10" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A10" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="H10" s="2">
+        <v>3</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="J10" s="2"/>
+    </row>
+    <row r="11" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A11" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="H11" s="2">
+        <v>4</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="J11" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30B98DFE-F155-4524-8A50-51FAE04C2BF7}">
+  <dimension ref="A1:J11"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="11.81640625" customWidth="1"/>
+    <col min="2" max="2" width="45.453125" style="7" customWidth="1"/>
+    <col min="3" max="3" width="21.81640625" style="7" customWidth="1"/>
+    <col min="4" max="7" width="34.54296875" style="7" customWidth="1"/>
+    <col min="8" max="8" width="10.90625" style="7" customWidth="1"/>
+    <col min="9" max="9" width="61.81640625" style="7" customWidth="1"/>
+    <col min="10" max="10" width="18.1796875" style="7" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="H2" s="2">
+        <v>3</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="J2" s="2"/>
+    </row>
+    <row r="3" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A3" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="H3" s="2">
+        <v>4</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="J3" s="2"/>
+    </row>
+    <row r="4" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A4" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="H4" s="2">
+        <v>1</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="J4" s="2"/>
+    </row>
+    <row r="5" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="H5" s="2">
+        <v>2</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="J5" s="2"/>
+    </row>
+    <row r="6" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A6" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="H6" s="2">
+        <v>3</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="J6" s="2"/>
+    </row>
+    <row r="7" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A7" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="H7" s="2">
+        <v>4</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="J7" s="2"/>
+    </row>
+    <row r="8" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A8" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="D8" s="6">
+        <v>0.27</v>
+      </c>
+      <c r="E8" s="6">
+        <v>1</v>
+      </c>
+      <c r="F8" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="G8" s="6">
+        <v>0</v>
+      </c>
+      <c r="H8" s="2">
+        <v>1</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="J8" s="2"/>
+    </row>
+    <row r="9" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A9" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="H9" s="2">
+        <v>2</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="J9" s="2"/>
+    </row>
+    <row r="10" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A10" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="H10" s="2">
+        <v>3</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="J10" s="2"/>
+    </row>
+    <row r="11" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A11" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="H11" s="2">
+        <v>4</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="J11" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x0101006B71C29808C7F3499BFFC3671560B6FA" ma:contentTypeVersion="8" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="e4f9e1976b194f932bebfa03c600f49f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="2aad7df3-4ab7-4daa-980d-cf7206357ce9" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8d33a1b74cd678b812bcd025038ca576" ns2:_="">
     <xsd:import namespace="2aad7df3-4ab7-4daa-980d-cf7206357ce9"/>
@@ -1184,14 +4706,57 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2aad7df3-4ab7-4daa-980d-cf7206357ce9">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{14B285EF-5CD0-4C6C-8B1E-1C411520A830}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D5E02106-BAAA-429E-8168-27D8ADC6435F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="2aad7df3-4ab7-4daa-980d-cf7206357ce9"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D79F9666-93FA-4B1C-A18B-FA6E74C38011}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D79F9666-93FA-4B1C-A18B-FA6E74C38011}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D5E02106-BAAA-429E-8168-27D8ADC6435F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{14B285EF-5CD0-4C6C-8B1E-1C411520A830}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="2aad7df3-4ab7-4daa-980d-cf7206357ce9"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Questions - Round 3.xlsx
+++ b/Questions - Round 3.xlsx
@@ -4543,8 +4543,8 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x0101006B71C29808C7F3499BFFC3671560B6FA" ma:contentTypeVersion="8" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="e4f9e1976b194f932bebfa03c600f49f">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="2aad7df3-4ab7-4daa-980d-cf7206357ce9" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8d33a1b74cd678b812bcd025038ca576" ns2:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101006B71C29808C7F3499BFFC3671560B6FA" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ff0b0af6195b7500cf034195288be193">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="2aad7df3-4ab7-4daa-980d-cf7206357ce9" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c14c416c1ab46b49649d30a0f512b68e" ns2:_="">
     <xsd:import namespace="2aad7df3-4ab7-4daa-980d-cf7206357ce9"/>
     <xsd:element name="properties">
       <xsd:complexType>
@@ -4589,7 +4589,7 @@
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Bildmarkierungen" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="9439331e-0c20-421d-a1f4-e02261aa89af" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="9439331e-0c20-421d-a1f4-e02261aa89af" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
@@ -4616,8 +4616,8 @@
         <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Inhaltstyp"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Titel"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
         <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
         <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
@@ -4726,21 +4726,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D5E02106-BAAA-429E-8168-27D8ADC6435F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="2aad7df3-4ab7-4daa-980d-cf7206357ce9"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{95AF89DE-9AF7-4404-9FE9-CD58A3316B54}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
